--- a/alicea_territory_chart.xlsx
+++ b/alicea_territory_chart.xlsx
@@ -2,29 +2,30 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisalicea\Documents\DATA_Labs\Capstone_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFD6805-FD8D-4D62-A6DB-0036583B84EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD113BB3-A222-42A0-A2DA-F7E1E1D98AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBD54DB2-1AEA-450D-8E42-A1DDF5E005D4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BBD54DB2-1AEA-450D-8E42-A1DDF5E005D4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="monthly_revenue" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="monthly_revenue" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>MonthlyRevenue</t>
   </si>
@@ -525,11 +526,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1159,7 +1164,730 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[alicea_territory_chart.xlsx]Sheet2!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$A$2:$A$54</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="48"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="28">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="29">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="30">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="31">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="32">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="33">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="34">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="35">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>1</c:v>
+                  </c:pt>
+                  <c:pt idx="37">
+                    <c:v>2</c:v>
+                  </c:pt>
+                  <c:pt idx="38">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="39">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="40">
+                    <c:v>5</c:v>
+                  </c:pt>
+                  <c:pt idx="41">
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="42">
+                    <c:v>7</c:v>
+                  </c:pt>
+                  <c:pt idx="43">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="44">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="45">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="46">
+                    <c:v>11</c:v>
+                  </c:pt>
+                  <c:pt idx="47">
+                    <c:v>12</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>2022</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>2023</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>2024</c:v>
+                  </c:pt>
+                  <c:pt idx="36">
+                    <c:v>2025</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$2:$B$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="48"/>
+                <c:pt idx="0">
+                  <c:v>58635.53</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60262.97</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>57143.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56880.02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>51805.22</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60549.86</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>56250.74</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>55052.53</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>60495.63</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56896.98</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>58402.69</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>55006.46</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>85210.01</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>86906.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>79964.160000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>97173.99</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>101370.73</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>83465.899999999994</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>90818.8</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>89422.22</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>89196.88</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>85095.72</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>79627.33</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>75904.66</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>94306.43</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>75083.7</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>99439.5</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>99105.22</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>87328.99</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>86955.71</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>89422.22</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>91189.41</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>83103.19</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>80543.34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>74988.649999999994</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>85210.01</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>135193.89000000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>104990.83</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>119415.67999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>117652.02</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>119352.07</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>135192.03</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>126976.23</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>133776.6</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>119597</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>185241.67</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>126941.06</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>128272.56</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3275-46A4-9EA9-F5C373357B1E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="553802624"/>
+        <c:axId val="441996528"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="553802624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="441996528"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="441996528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="553802624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1702,6 +2430,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1723,6 +2954,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CC66835-AAA1-94D2-7E14-95CFF8ADEA12}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAD98462-52B1-F33B-3D72-10CACD18784A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2031,7 +3303,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63DDDF03-F83C-41C0-A85B-6C24995A3A84}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{63DDDF03-F83C-41C0-A85B-6C24995A3A84}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" showAll="0"/>
@@ -2077,6 +3349,232 @@
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of MonthlyRevenue" fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B5CC1389-7F40-4E8E-A070-F423C4B351B7}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A1:B54" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="53">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
     </i>
     <i t="grand">
       <x/>
@@ -2491,6 +3989,453 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696E0A79-DBCA-409E-B701-255A8854F71B}">
+  <dimension ref="A1:B54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B2" s="3">
+        <v>687382.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3">
+        <v>58635.53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3">
+        <v>60262.97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3">
+        <v>57143.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3">
+        <v>56880.02</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3">
+        <v>51805.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>60549.86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>56250.74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3">
+        <v>55052.53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3">
+        <v>60495.63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3">
+        <v>56896.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3">
+        <v>58402.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3">
+        <v>55006.46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1044157.0499999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
+        <v>1</v>
+      </c>
+      <c r="B16" s="3">
+        <v>85210.01</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3">
+        <v>86906.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3">
+        <v>79964.160000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4">
+        <v>4</v>
+      </c>
+      <c r="B19" s="3">
+        <v>97173.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3">
+        <v>101370.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4">
+        <v>6</v>
+      </c>
+      <c r="B21" s="3">
+        <v>83465.899999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4">
+        <v>7</v>
+      </c>
+      <c r="B22" s="3">
+        <v>90818.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3">
+        <v>89422.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4">
+        <v>9</v>
+      </c>
+      <c r="B24" s="3">
+        <v>89196.88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4">
+        <v>10</v>
+      </c>
+      <c r="B25" s="3">
+        <v>85095.72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4">
+        <v>11</v>
+      </c>
+      <c r="B26" s="3">
+        <v>79627.33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4">
+        <v>12</v>
+      </c>
+      <c r="B27" s="3">
+        <v>75904.66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1046676.3699999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4">
+        <v>1</v>
+      </c>
+      <c r="B29" s="3">
+        <v>94306.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="4">
+        <v>2</v>
+      </c>
+      <c r="B30" s="3">
+        <v>75083.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4">
+        <v>3</v>
+      </c>
+      <c r="B31" s="3">
+        <v>99439.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3">
+        <v>99105.22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="4">
+        <v>5</v>
+      </c>
+      <c r="B33" s="3">
+        <v>87328.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="4">
+        <v>6</v>
+      </c>
+      <c r="B34" s="3">
+        <v>86955.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="4">
+        <v>7</v>
+      </c>
+      <c r="B35" s="3">
+        <v>89422.22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="4">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3">
+        <v>91189.41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="4">
+        <v>9</v>
+      </c>
+      <c r="B37" s="3">
+        <v>83103.19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>10</v>
+      </c>
+      <c r="B38" s="3">
+        <v>80543.34</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4">
+        <v>11</v>
+      </c>
+      <c r="B39" s="3">
+        <v>74988.649999999994</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4">
+        <v>12</v>
+      </c>
+      <c r="B40" s="3">
+        <v>85210.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B41" s="3">
+        <v>1552601.6400000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4">
+        <v>1</v>
+      </c>
+      <c r="B42" s="3">
+        <v>135193.89000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="4">
+        <v>2</v>
+      </c>
+      <c r="B43" s="3">
+        <v>104990.83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="4">
+        <v>3</v>
+      </c>
+      <c r="B44" s="3">
+        <v>119415.67999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>4</v>
+      </c>
+      <c r="B45" s="3">
+        <v>117652.02</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>5</v>
+      </c>
+      <c r="B46" s="3">
+        <v>119352.07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="4">
+        <v>6</v>
+      </c>
+      <c r="B47" s="3">
+        <v>135192.03</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="4">
+        <v>7</v>
+      </c>
+      <c r="B48" s="3">
+        <v>126976.23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="4">
+        <v>8</v>
+      </c>
+      <c r="B49" s="3">
+        <v>133776.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="4">
+        <v>9</v>
+      </c>
+      <c r="B50" s="3">
+        <v>119597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="4">
+        <v>10</v>
+      </c>
+      <c r="B51" s="3">
+        <v>185241.67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4">
+        <v>11</v>
+      </c>
+      <c r="B52" s="3">
+        <v>126941.06</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="4">
+        <v>12</v>
+      </c>
+      <c r="B53" s="3">
+        <v>128272.56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="3">
+        <v>4330817.09</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDB5EE09-6F58-4FCA-A599-17C746EB2F38}">
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
